--- a/模板_成本差异分析表.xlsx
+++ b/模板_成本差异分析表.xlsx
@@ -456,56 +456,62 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16.3" customWidth="1" min="1" max="1"/>
-    <col width="13.7" customWidth="1" min="2" max="2"/>
-    <col width="21.5" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="17.6" customWidth="1" min="2" max="2"/>
+    <col width="13.7" customWidth="1" min="3" max="3"/>
+    <col width="21.5" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="8.5" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8.5" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>物料编码</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>品名</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>规格型号</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>单位</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>标准单价</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>标准用量</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>标准总成本</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>单位</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -514,162 +520,257 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>MAT-IC-001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>芯片IC-A</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>STM32F407VGT6</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="n">
         <v>12.5</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="G2" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="H2" s="2" t="n">
         <v>6250</v>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>个</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
           <t>MAT-CAP-002</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>电容B-100uF</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>16V 贴片 0805</t>
         </is>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="n">
         <v>0.85</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="G3" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="H3" s="3" t="n">
         <v>2550</v>
       </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>个</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>MAT-PCB-003</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>PCB板4层</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>FR-4 100x80mm</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>块</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="G4" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="H4" s="2" t="n">
         <v>5600</v>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>块</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
           <t>MAT-CON-004</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>连接器TypeC</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>USB-C 16P 沉板</t>
         </is>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="n">
         <v>3.2</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="G5" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="H5" s="3" t="n">
         <v>2560</v>
       </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>个</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>MAT-HS-005</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>散热片铝</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>AL6063 40x40x20</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="G6" s="2" t="n">
         <v>400</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="H6" s="2" t="n">
         <v>1800</v>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>个</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>LAB-ASM-001</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>SMT贴片人工</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>点</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>外协</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>LAB-TEST-002</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>测试检验人工</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>点</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -682,56 +783,62 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16.3" customWidth="1" min="1" max="1"/>
-    <col width="13.7" customWidth="1" min="2" max="2"/>
-    <col width="21.5" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="17.6" customWidth="1" min="2" max="2"/>
+    <col width="13.7" customWidth="1" min="3" max="3"/>
+    <col width="21.5" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="8.5" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="8.5" customWidth="1" min="8" max="8"/>
+    <col width="8.5" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>物料编码</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>品名</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>规格型号</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>单位</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>标准单价</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>标准用量</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>标准总成本</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>单位</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -740,34 +847,39 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>MAT-IC-001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>芯片IC-A</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>STM32F407VGT6</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="n">
         <v>14.2</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="G2" s="2" t="n">
         <v>480</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="H2" s="2" t="n">
         <v>6816</v>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>个</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>供应商涨价</t>
         </is>
@@ -776,130 +888,220 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
           <t>MAT-CAP-002</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>电容B-100uF</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>16V 贴片 0805</t>
         </is>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="n">
         <v>0.82</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="G3" s="3" t="n">
         <v>3100</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="H3" s="3" t="n">
         <v>2542</v>
       </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>个</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>MAT-PCB-003</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>PCB板4层</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>FR-4 100x80mm</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>块</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="G4" s="2" t="n">
         <v>195</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="H4" s="2" t="n">
         <v>5460</v>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>块</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
           <t>MAT-CON-004</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>连接器TypeC</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>USB-C 16P 沉板</t>
         </is>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="G5" s="3" t="n">
         <v>780</v>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="H5" s="3" t="n">
         <v>2730</v>
       </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>个</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>MAT-HS-005</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>散热片铝</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>AL6063 40x40x20</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="n">
         <v>4.3</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="G6" s="2" t="n">
         <v>420</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="H6" s="2" t="n">
         <v>1806</v>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>个</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>LAB-ASM-001</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>SMT贴片人工</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>点</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>5200</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>442</v>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>效率提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>LAB-TEST-002</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>测试检验人工</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>点</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>1900</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>228</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/模板_成本差异分析表.xlsx
+++ b/模板_成本差异分析表.xlsx
@@ -456,13 +456,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="17.6" customWidth="1" min="2" max="2"/>
+    <col width="16.3" customWidth="1" min="2" max="2"/>
     <col width="13.7" customWidth="1" min="3" max="3"/>
-    <col width="21.5" customWidth="1" min="4" max="4"/>
+    <col width="18.9" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
@@ -572,7 +572,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>16V 贴片 0805</t>
+          <t>16V 0805</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>USB-C 16P 沉板</t>
+          <t>USB-C 16P</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>AL6063 40x40x20</t>
+          <t>AL6063 40x40</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -701,76 +701,6 @@
         <v>1800</v>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>2024-06-01</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>LAB-ASM-001</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>SMT贴片人工</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>点</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>400</v>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>外协</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>2024-06-01</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>LAB-TEST-002</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>测试检验人工</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr"/>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>点</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>2000</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>240</v>
-      </c>
-      <c r="I8" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -783,15 +713,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="17.6" customWidth="1" min="2" max="2"/>
+    <col width="16.3" customWidth="1" min="2" max="2"/>
     <col width="13.7" customWidth="1" min="3" max="3"/>
-    <col width="21.5" customWidth="1" min="4" max="4"/>
+    <col width="18.9" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="8.5" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="8.5" customWidth="1" min="8" max="8"/>
     <col width="8.5" customWidth="1" min="9" max="9"/>
@@ -903,7 +833,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>16V 贴片 0805</t>
+          <t>16V 0805</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -977,7 +907,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>USB-C 16P 沉板</t>
+          <t>USB-C 16P</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -1014,7 +944,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>AL6063 40x40x20</t>
+          <t>AL6063 40x40</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1032,76 +962,6 @@
         <v>1806</v>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>2024-06-01</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>LAB-ASM-001</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>SMT贴片人工</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>点</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>0.08500000000000001</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>5200</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>442</v>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>效率提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>2024-06-01</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>LAB-TEST-002</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>测试检验人工</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr"/>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>点</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>1900</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>228</v>
-      </c>
-      <c r="I8" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/模板_成本差异分析表.xlsx
+++ b/模板_成本差异分析表.xlsx
@@ -755,17 +755,17 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>标准单价</t>
+          <t>实际单价</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>标准用量</t>
+          <t>实际用量</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>标准总成本</t>
+          <t>实际总成本</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
